--- a/etf_holdings/2026-10-14_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-14_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB9"/>
+  <dimension ref="A1:AR8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,100 +589,50 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>00990A_異動類型</t>
+          <t>00400A_異動類型</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>00990A_調整方向</t>
+          <t>00400A_調整方向</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>00990A_股票名稱_昨日</t>
+          <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>00990A_股票名稱_今日</t>
+          <t>00400A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>00990A_權重_昨日</t>
+          <t>00400A_權重_昨日</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>00990A_權重_今日</t>
+          <t>00400A_權重_今日</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>00990A_權重變化</t>
+          <t>00400A_權重變化</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>00990A_股數_昨日</t>
+          <t>00400A_股數_昨日</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>00990A_股數_今日</t>
+          <t>00400A_股數_今日</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
-        <is>
-          <t>00990A_股數變化</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>00400A_異動類型</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>00400A_調整方向</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>00400A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>00400A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>00400A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>00400A_權重_今日</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>00400A_權重變化</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>00400A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>00400A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -805,58 +755,48 @@
           <t>92,000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>1.20%</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>1.70%</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>+0.50%</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AP2" t="n">
         <v>51000</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="AQ2" t="n">
         <v>71000</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -983,58 +923,48 @@
           <t>-800,000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>4.89%</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>4.15%</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>-0.74%</t>
         </is>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AP3" t="n">
         <v>1209000</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="AQ3" t="n">
         <v>1069000</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>-140,000</t>
         </is>
@@ -1121,58 +1051,48 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>4.10%</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>2.77%</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>-1.33%</t>
         </is>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AP4" t="n">
         <v>669000</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="AQ4" t="n">
         <v>475000</v>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>-194,000</t>
         </is>
@@ -1263,58 +1183,48 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>台積電</t>
         </is>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>8.47%</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>8.96%</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>+0.49%</t>
         </is>
       </c>
-      <c r="AZ5" t="n">
+      <c r="AP5" t="n">
         <v>1034000</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="AQ5" t="n">
         <v>1094000</v>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>60,000</t>
         </is>
@@ -1323,12 +1233,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1336,19 +1246,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00400A,00990A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>00400A,00981A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9.81%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8.53%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-1.28%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4328000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-322,000</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1371,88 +1317,60 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>5.59%</t>
+        </is>
+      </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>-0.96%</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>282000</v>
+      </c>
       <c r="AQ6" t="n">
-        <v>156000</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1.51%</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>+0.44%</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>378000</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>507000</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>129,000</t>
+        <v>254000</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-28,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1470,43 +1388,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9.81%</t>
+          <t>7.04%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>7.17%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4650000</v>
+        <v>6062000</v>
       </c>
       <c r="M7" t="n">
-        <v>4328000</v>
+        <v>6147000</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-322,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1529,72 +1447,62 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>5.59%</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4.63%</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>-0.96%</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>282000</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>254000</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-28,000</t>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>4.12%</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>-0.57%</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>377000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>329000</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-48,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1602,7 +1510,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00400A,00981A</t>
+          <t>00403A,00981A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1617,38 +1525,38 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.17%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6062000</v>
+        <v>476000</v>
       </c>
       <c r="M8" t="n">
-        <v>6147000</v>
+        <v>576000</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1661,16 +1569,52 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2.32%</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1681,194 +1625,6 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>4.12%</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3.55%</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>-0.57%</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>377000</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>329000</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-48,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>476000</v>
-      </c>
-      <c r="M9" t="n">
-        <v>576000</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2.16%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2.32%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1880000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>80,000</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/etf_holdings/2026-10-14_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-14_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:BV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,150 +439,350 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>00981A_異動類型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>00981A_調整方向</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>00981A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>00981A_權重_今日</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>00981A_權重變化</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>00981A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>00981A_股數_今日</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>00981A_股數變化</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>00403A_異動類型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00403A_調整方向</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00403A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00403A_權重_昨日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00403A_權重_今日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00403A_權重變化</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00403A_股數_昨日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00403A_股數_今日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00403A_股數變化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>00990A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00990A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00990A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00990A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00990A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00990A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00990A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00990A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00990A_股數變化</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>00407A_異動類型</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>00407A_調整方向</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>00407A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>00407A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>00407A_權重變化</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>00407A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>00407A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>00407A_股數變化</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>00993A_異動類型</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>00993A_調整方向</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>00993A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>00993A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>00993A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>00993A_權重_今日</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>00993A_權重變化</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>00993A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>00993A_股數_今日</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>00993A_股數變化</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -600,173 +800,303 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00400A,00990A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+          <t>00400A,00407A,00981A,00990A,00993A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>+0.84%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>3741000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5423000</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1,682,000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
         <v>156000</v>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>金像電</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>金像電</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>+0.73%</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>113000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>236000</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>123,000</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="n">
+        <v>26000</v>
+      </c>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>1.51%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>+0.44%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
         <v>378000</v>
       </c>
-      <c r="AG2" t="n">
-        <v>507000</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>129,000</t>
+      <c r="BU2" t="n">
+        <v>734000</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>356,000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00403A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>00400A,00403A,00991A,00993A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.75%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>+0.51%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>243000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>335000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>92,000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>8.60%</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>-8.56%</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>5280000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>70,000</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -774,63 +1104,175 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6.83%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5.95%</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>-0.88%</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-800,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1.20%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>+0.50%</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>51000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>71000</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>20,000</t>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>6.26%</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="BJ3" t="n">
+        <v>518000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>526000</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>4.11%</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>-0.78%</t>
+        </is>
+      </c>
+      <c r="BT3" t="n">
+        <v>1209000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-140,000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00400A,00403A</t>
+          <t>00403A,00407A,00981A,00990A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -840,43 +1282,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.83%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7800000</v>
+        <v>684000</v>
       </c>
       <c r="M4" t="n">
-        <v>7000000</v>
+        <v>751000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-800,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -896,45 +1338,2943 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>3.87%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>640000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>655000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>23000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4.89%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>4.15%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-0.74%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>1209000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1069000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-140,000</t>
-        </is>
-      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>5.02%</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>4.72%</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>143000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>128000</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00403A,00407A,00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>476000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>696000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>220,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>-1.06%</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>324000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>179000</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-145,000</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00400A,00990A,00991A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>-1.64%</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>650000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>-649,000</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>3.33%</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>-1.29%</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>633000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>420000</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-213,000</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>2.75%</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-1.35%</t>
+        </is>
+      </c>
+      <c r="BT6" t="n">
+        <v>669000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>475000</v>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>-194,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00400A,00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10.30%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10.73%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>11824000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12188000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>364,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>8.35%</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>8.26%</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>341000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>333000</v>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>8.47%</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>8.85%</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="BT7" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00400A,00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9.81%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8.45%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4328000</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-322,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>6.27%</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>6.23%</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>106000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>113000</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>5.59%</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>-1.04%</t>
+        </is>
+      </c>
+      <c r="BT8" t="n">
+        <v>282000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>254000</v>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>-28,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00400A,00403A,00991A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>130000</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>129,000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
+        <v>243000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>335000</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>92,000</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="BT9" t="n">
+        <v>51000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>71000</v>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00403A,00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>6771000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6847000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>76,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2.54%</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2180000</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>80,000</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>4.07%</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>244000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>249000</v>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>1.79%</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00400A,00403A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>-5,000,000</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>+0.95%</t>
+        </is>
+      </c>
+      <c r="BT12" t="n">
+        <v>2096000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4192000</v>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>2,096,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>400,000</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>185000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>189000</v>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00403A,00993A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>350000</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-950,000</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="n">
+        <v>159000</v>
+      </c>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00400A,00981A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7.21%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>6062000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6147000</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>85,000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>4.12%</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="BT15" t="n">
+        <v>377000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>329000</v>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>-48,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00400A,00993A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>134000</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>136000</v>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="BT16" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1287000</v>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>253,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>+0.12%</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1257000</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1,256,000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>214000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>219000</v>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>157900</v>
+      </c>
+      <c r="M18" t="n">
+        <v>186900</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>29,000</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>+0.38%</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>117500</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>145500</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>28,000</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00400A,00993A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>121000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>125000</v>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>-1.74%</t>
+        </is>
+      </c>
+      <c r="BT19" t="n">
+        <v>596000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>295000</v>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>-301,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00981A,00993A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2.45%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>4315561</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3281561</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-1,034,000</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>4.27%</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>-2.10%</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>195191</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>99191</v>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>-96,000</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
